--- a/spider_wd/评价数据.xlsx
+++ b/spider_wd/评价数据.xlsx
@@ -1,195 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="评论" sheetId="1" r:id="rId1"/>
+    <sheet name="评论" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -490,153 +472,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -690,11 +672,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -981,15 +1026,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="16384"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>实力一点没有就是硬装[哆啦A梦害怕]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>刷流量而已[笑cry]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>没有哪个作弊的人敢说出来，唯一敢说的就是摆拍获取流量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>能花钱摆平高考作弊的，不会在乎高考[允悲]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>为了流量不择手段</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>众所周知，真正要运作的，不会等到作弊被抓再运作[并不简单]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>没事，家里有钱将来也是某公司的高管[打call]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>想也知道是摆拍，真有这事儿谁会承认还接受采访[doge]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>拘留几天就老实了</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>这个也敢摆拍[怒]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建议直接拘他#情况通报# </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>哪个平台的？这个平台审核视频的门槛是什么？针对社会性内容的审核难道不应该严肃认真对待？平台需要反思。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>那些上本科重点大学用💰走后门的咋不说[二哈][二哈][二哈]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>我同学就是高考移民，考最后一课时拿出手机被查了，家长找关系让他第二年接着考</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>纯有🧊@kinovasy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>又是为了流量不择手段的摆拍...</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>#高考生作弊家长用钱摆平系摆拍#什么心理啊，我想问问这个处理结果是什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>虚荣心害人害己</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>抓了么</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>是真摆平了 还是博流量[汗]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>这可比找到寒假作业本严重</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>，</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>！</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>转发微博</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>//@全是狗粮呀:实力一点没有就是硬装[哆啦A梦害怕]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>还是吃的太饱了[doge]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>高考作弊姓陈名鹏的最知道了</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>抓紧去蹲几天就老实了</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>作弊的多了去了，我高考的时候，亲眼看到有人直接飞纸条给答案，老师睁一只眼闭一只眼，看完那个作弊的还给老师递烟[允悲]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>不抓吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>建议以寻衅滋事罪追究刑事责任 维护高考严肃性是最大的公序良俗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>这下好了，估计要进去吃几天牢饭[吃瓜] #高考生作弊家长用钱摆平系摆拍#</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>善不可不弘，恶不可不去。 善心人人有，快乐你我他。 善念养善心，善心生善念。 德不积不厚，善不行不成。 人往高处走，善在心中留。 至宝不常现，至善不常有。 行莫于恭敬，善莫于用心。 由善入恶易，由恶入善难。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>生活是有光的，你得跑起来，跑得远些就能看见，总有一束光会打在你身上</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>毫无底线了</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>摆拍</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>